--- a/backend/data/ST2131_Questions.xlsx
+++ b/backend/data/ST2131_Questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9291B3CC-0A13-E646-B31B-63A79AC4FED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AAAE61-C6AC-D34A-9BA7-568B1B10A224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Context" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="136">
   <si>
-    <t>Context ID</t>
-  </si>
-  <si>
     <t>Context Text</t>
   </si>
   <si>
@@ -491,6 +488,9 @@
   </si>
   <si>
     <t>Random Variables</t>
+  </si>
+  <si>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -879,13 +879,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -908,52 +908,52 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>3024</v>
@@ -976,16 +976,16 @@
         <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" t="s">
         <v>106</v>
-      </c>
-      <c r="O2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -993,31 +993,31 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="187" x14ac:dyDescent="0.2">
@@ -1025,31 +1025,31 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
         <v>0.5</v>
       </c>
       <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1057,10 +1057,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1069,16 +1069,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -1086,31 +1086,31 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -1118,10 +1118,10 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1130,19 +1130,19 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1150,31 +1150,31 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1182,10 +1182,10 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1194,16 +1194,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1211,31 +1211,31 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" t="s">
         <v>38</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -1243,31 +1243,31 @@
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -1275,10 +1275,10 @@
         <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>0.42</v>
@@ -1290,16 +1290,16 @@
         <v>0.24</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1307,31 +1307,31 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>49</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>50</v>
       </c>
-      <c r="H13" t="s">
-        <v>51</v>
-      </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -1339,22 +1339,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="204" x14ac:dyDescent="0.2">
@@ -1362,25 +1362,25 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
         <v>54</v>
       </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -1388,10 +1388,10 @@
         <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1417,31 +1417,31 @@
         <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
         <v>59</v>
       </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>60</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>61</v>
       </c>
-      <c r="H17" t="s">
-        <v>62</v>
-      </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="51" x14ac:dyDescent="0.2">
@@ -1449,33 +1449,33 @@
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1483,31 +1483,31 @@
         <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" t="s">
         <v>67</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>68</v>
       </c>
-      <c r="H19" t="s">
-        <v>69</v>
-      </c>
       <c r="K19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="51" x14ac:dyDescent="0.2">
@@ -1515,10 +1515,10 @@
         <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -1527,16 +1527,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1544,31 +1544,31 @@
         <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
         <v>71</v>
       </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>72</v>
-      </c>
       <c r="G21" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" t="s">
         <v>68</v>
       </c>
-      <c r="H21" t="s">
-        <v>69</v>
-      </c>
       <c r="K21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="85" x14ac:dyDescent="0.2">
@@ -1576,10 +1576,10 @@
         <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22">
         <v>0.79</v>
@@ -1591,16 +1591,16 @@
         <v>0.3</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1608,13 +1608,13 @@
         <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
         <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" t="s">
-        <v>75</v>
       </c>
       <c r="G23">
         <v>0.06</v>
@@ -1623,16 +1623,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M23">
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="2:15" ht="85" x14ac:dyDescent="0.2">
@@ -1640,10 +1640,10 @@
         <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24">
         <v>6720</v>
@@ -1655,16 +1655,16 @@
         <v>480</v>
       </c>
       <c r="K24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="2:15" ht="17" x14ac:dyDescent="0.2">
@@ -1672,10 +1672,10 @@
         <v>37</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>6720</v>
@@ -1687,16 +1687,16 @@
         <v>480</v>
       </c>
       <c r="K25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="2:15" ht="102" x14ac:dyDescent="0.2">
@@ -1704,31 +1704,31 @@
         <v>38</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
         <v>78</v>
       </c>
-      <c r="E26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>79</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>80</v>
       </c>
-      <c r="H26" t="s">
-        <v>81</v>
-      </c>
       <c r="K26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1736,31 +1736,31 @@
         <v>41</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s">
         <v>82</v>
       </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>83</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>84</v>
       </c>
-      <c r="H27" t="s">
-        <v>85</v>
-      </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="68" x14ac:dyDescent="0.2">
@@ -1768,33 +1768,33 @@
         <v>42</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="68" x14ac:dyDescent="0.2">
@@ -1802,33 +1802,33 @@
         <v>43</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="34" x14ac:dyDescent="0.2">
@@ -1836,31 +1836,31 @@
         <v>44</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="E30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>92</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>93</v>
       </c>
-      <c r="H30" t="s">
-        <v>94</v>
-      </c>
       <c r="K30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="51" x14ac:dyDescent="0.2">
@@ -1868,10 +1868,10 @@
         <v>45</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1880,16 +1880,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="17" x14ac:dyDescent="0.2">
@@ -1897,10 +1897,10 @@
         <v>46</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1909,16 +1909,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="85" x14ac:dyDescent="0.2">
@@ -1926,10 +1926,10 @@
         <v>47</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33">
         <v>0.69</v>
@@ -1941,16 +1941,16 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="68" x14ac:dyDescent="0.2">
@@ -1958,31 +1958,31 @@
         <v>48</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
         <v>98</v>
       </c>
-      <c r="E34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>99</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>100</v>
       </c>
-      <c r="H34" t="s">
-        <v>101</v>
-      </c>
       <c r="K34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.2">
